--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allowed coded values for Medications, generated from enum_models.py.</t>
+    <t>Allowed coded values for Medications</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>Nimodipine (substance)</t>
+  </si>
+  <si>
+    <t>372912004</t>
+  </si>
+  <si>
+    <t>Substance with 3-hydroxy-3-methylglutaryl-coenzyme A reductase inhibitor mechanism of action (substance)</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
@@ -622,7 +628,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -823,18 +829,26 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>39</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>88</v>
+      <c r="B27" t="s" s="2">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,6 +131,12 @@
   </si>
   <si>
     <t>No Medication</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Other Medication</t>
   </si>
   <si>
     <t/>
@@ -550,7 +556,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -610,15 +616,23 @@
         <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -645,210 +659,210 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/medications-vs</t>
+    <t>http://qualityregistry.org/ValueSet/medications-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -73,7 +73,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -145,7 +145,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/medication-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/medication-cs</t>
   </si>
   <si>
     <t>372586001</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-medications-vs.xlsx
+++ b/ValueSet-medications-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
